--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1229"/>
+  <dimension ref="A1:J1230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42271,6 +42271,40 @@
         <v>0.396</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B1230" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1230" s="3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D1230" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E1230" s="3" t="n">
+        <v>4.386</v>
+      </c>
+      <c r="F1230" s="3" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="G1230" s="3" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="H1230" s="3" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="I1230" s="3" t="n">
+        <v>2.893</v>
+      </c>
+      <c r="J1230" s="3" t="n">
+        <v>0.393</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1230"/>
+  <dimension ref="A1:J1231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42305,6 +42305,40 @@
         <v>0.384</v>
       </c>
     </row>
+    <row r="1231">
+      <c r="A1231" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B1231" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1231" s="3" t="n">
+        <v>3.736</v>
+      </c>
+      <c r="D1231" s="3" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="E1231" s="3" t="n">
+        <v>4.361</v>
+      </c>
+      <c r="F1231" s="3" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="G1231" s="3" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="H1231" s="3" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="I1231" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J1231" s="3" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1229"/>
+  <dimension ref="A1:J1230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42271,6 +42271,40 @@
         <v>0.456</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B1230" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1230" s="3" t="n">
+        <v>3.731</v>
+      </c>
+      <c r="D1230" s="3" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="E1230" s="3" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="F1230" s="3" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="G1230" s="3" t="n">
+        <v>3.343</v>
+      </c>
+      <c r="H1230" s="3" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="I1230" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J1230" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.489</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.773</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.402</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>2.991</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.491</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.491</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.858</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.456</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.537</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.882</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.501</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>2.001</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.483</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.548</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.587</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.856</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.492</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.516</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.57</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.881</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.999</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.536</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.569</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.569</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.904</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.552</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.074</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.574</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.933</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.527</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.505</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.784</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.419</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.024</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.524</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.531</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.917</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.584</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.525</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.772</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.928</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.531</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.531</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.757</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.403</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.903</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.605</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.522</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.522</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.722</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.611</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.523</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.703</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.634</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.522</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.594</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.747</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.931</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.665</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.272</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.772</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.772</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.748</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.933</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.674</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.279</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.779</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.779</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.776</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.459</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.959</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.682</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.787</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.787</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.472</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.701</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.295</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.795</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.473</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.706</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.293</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.793</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.793</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.778</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.478</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.711</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.292</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.792</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1228"/>
+  <dimension ref="A1:J1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42237,6 +42237,40 @@
         <v>0.792</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>3.768</v>
+      </c>
+      <c r="D1229" s="3" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="E1229" s="3" t="n">
+        <v>4.466</v>
+      </c>
+      <c r="F1229" s="3" t="n">
+        <v>1.966</v>
+      </c>
+      <c r="G1229" s="3" t="n">
+        <v>3.709</v>
+      </c>
+      <c r="H1229" s="3" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="I1229" s="3" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="J1229" s="3" t="n">
+        <v>0.787</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.798</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.887</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.582</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>2.082</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.755</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.331</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.831</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.831</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.866</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.563</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>2.063</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.734</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.324</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.824</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.544</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.305</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.5669999999999999</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.571</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.301</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.551</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.604</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.569</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.959</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.653</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.903</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.541</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.636</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.525</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.831</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.541</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.53</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.758</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.478</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.261</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.511</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.742</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.462</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.712</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.501</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.501</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.458</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.599</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.502</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.669</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.392</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.48</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.742</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.445</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.595</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.248</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.498</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.498</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.746</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.448</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.698</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.593</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.245</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.495</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.495</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.778</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.599</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.502</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.504</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.613</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.513</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.513</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.791</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.496</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.746</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.614</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.264</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.514</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.514</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.781</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.507</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.507</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.796</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.492</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.618</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.262</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.512</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.642</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.265</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.515</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.497</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.811</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.504</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.649</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.259</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.509</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.509</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.664</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.274</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.524</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.524</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.666</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.266</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.516</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.516</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.516</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.766</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.675</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.518</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.816</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.276</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.526</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.526</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.755</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.448</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.671</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.693</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1226"/>
+  <dimension ref="A1:J1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42169,6 +42169,40 @@
         <v>0.278</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>3.878</v>
+      </c>
+      <c r="D1227" s="3" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="E1227" s="3" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="F1227" s="3" t="n">
+        <v>1.549</v>
+      </c>
+      <c r="G1227" s="3" t="n">
+        <v>3.722</v>
+      </c>
+      <c r="H1227" s="3" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="I1227" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J1227" s="3" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.268</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>3.884</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.278</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spread.xlsx
+++ b/spread.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1227"/>
+  <dimension ref="A1:J1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42203,6 +42203,40 @@
         <v>0.323</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>4.014</v>
+      </c>
+      <c r="D1228" s="3" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="E1228" s="3" t="n">
+        <v>4.688</v>
+      </c>
+      <c r="F1228" s="3" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="G1228" s="3" t="n">
+        <v>3.843</v>
+      </c>
+      <c r="H1228" s="3" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="I1228" s="3" t="n">
+        <v>3.359</v>
+      </c>
+      <c r="J1228" s="3" t="n">
+        <v>0.359</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
